--- a/data/gravel/Wilier Jena 2025.xlsx
+++ b/data/gravel/Wilier Jena 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4F9055-FDA5-C04B-B72F-6A5B40523493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E4469F-488D-BA46-9A08-B6BE4717622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22500" yWindow="-20420" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>a8:g33</t>
+  </si>
+  <si>
+    <t>https://bikeinsights.com/bikes/5e134a7e61f091001796de41-wilier-triestina-jena</t>
   </si>
 </sst>
 </file>
@@ -1189,6 +1192,9 @@
       <c r="G19">
         <v>70</v>
       </c>
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">

--- a/data/gravel/Wilier Jena 2025.xlsx
+++ b/data/gravel/Wilier Jena 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E4469F-488D-BA46-9A08-B6BE4717622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19526CE8-36C1-C44C-867A-7109378DCA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22500" yWindow="-20420" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33380" yWindow="-24120" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,13 +348,19 @@
   </si>
   <si>
     <t>https://bikeinsights.com/bikes/5e134a7e61f091001796de41-wilier-triestina-jena</t>
+  </si>
+  <si>
+    <t>fiji estimate</t>
+  </si>
+  <si>
+    <t>43.7fiji estimate41</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -369,6 +375,13 @@
     <font>
       <sz val="14"/>
       <name val="Futura Medium"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -391,11 +404,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1199,17 +1213,77 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="C21" s="1">
+        <v>44</v>
+      </c>
+      <c r="D21" s="1">
+        <v>44</v>
+      </c>
+      <c r="E21" s="1">
+        <v>44</v>
+      </c>
+      <c r="F21" s="1">
+        <v>44</v>
+      </c>
+      <c r="G21" s="1">
+        <v>44</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I21">
+        <v>41.738999999999997</v>
+      </c>
+      <c r="J21">
+        <v>36.651000000000003</v>
+      </c>
+      <c r="K21">
+        <v>51.341000000000001</v>
+      </c>
+      <c r="L21">
+        <v>47.198</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
+      </c>
+      <c r="C22" s="1">
+        <v>400</v>
+      </c>
+      <c r="D22" s="1">
+        <v>400</v>
+      </c>
+      <c r="E22" s="1">
+        <v>400</v>
+      </c>
+      <c r="F22" s="1">
+        <v>400</v>
+      </c>
+      <c r="G22" s="1">
+        <v>400</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="1">
+        <v>401.65899999999999</v>
+      </c>
+      <c r="J22" s="1">
+        <v>402.875</v>
+      </c>
+      <c r="K22">
+        <v>399.596</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">

--- a/data/gravel/Wilier Jena 2025.xlsx
+++ b/data/gravel/Wilier Jena 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19526CE8-36C1-C44C-867A-7109378DCA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219C65AA-DCBC-C94C-8B94-C3046F1EAB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33380" yWindow="-24120" windowWidth="24520" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,24 @@
   </si>
   <si>
     <t>43.7fiji estimate41</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -706,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1511,164 +1529,194 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>71</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>73</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>74</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>68</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>79</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>80</v>
-      </c>
-      <c r="B66">
-        <v>3</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>83</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>54</v>
+        <v>77</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>85</v>
-      </c>
-      <c r="B71">
-        <v>2700</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>94</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>95</v>
       </c>
     </row>
